--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8147CA4-F776-44C7-B010-DE9F922313F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF86D915-8883-4297-A918-5605993EAF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>check_group</t>
   </si>
@@ -101,6 +101,18 @@
   </si>
   <si>
     <t>num_children_under5,</t>
+  </si>
+  <si>
+    <t>sexratio</t>
+  </si>
+  <si>
+    <t>ageratio</t>
+  </si>
+  <si>
+    <t>anova</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 8</t>
   </si>
 </sst>
 </file>
@@ -489,6 +501,15 @@
       <c r="D2" t="s">
         <v>16</v>
       </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -500,6 +521,15 @@
       <c r="D3" t="s">
         <v>17</v>
       </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -511,6 +541,15 @@
       <c r="D4" t="s">
         <v>26</v>
       </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -522,6 +561,15 @@
       <c r="D5" t="s">
         <v>18</v>
       </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -533,6 +581,15 @@
       <c r="D6" t="s">
         <v>19</v>
       </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -544,6 +601,15 @@
       <c r="D7" t="s">
         <v>25</v>
       </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -555,6 +621,15 @@
       <c r="D8" t="s">
         <v>24</v>
       </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -566,6 +641,15 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -576,6 +660,15 @@
       </c>
       <c r="D10" t="s">
         <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF86D915-8883-4297-A918-5605993EAF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E526EE6C-97AF-46FA-81B0-50C1C051EEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21255" yWindow="3210" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
   <si>
     <t>check_group</t>
   </si>
@@ -113,6 +113,33 @@
   </si>
   <si>
     <t>test_statistic &lt; 8</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>i</t>
   </si>
 </sst>
 </file>
@@ -457,7 +484,7 @@
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
     <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -498,6 +525,9 @@
       <c r="B2" t="s">
         <v>8</v>
       </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
@@ -518,6 +548,9 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
@@ -538,6 +571,9 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
       <c r="D4" t="s">
         <v>26</v>
       </c>
@@ -558,6 +594,9 @@
       <c r="B5" t="s">
         <v>11</v>
       </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
@@ -578,6 +617,9 @@
       <c r="B6" t="s">
         <v>12</v>
       </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
@@ -598,6 +640,9 @@
       <c r="B7" t="s">
         <v>13</v>
       </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
       <c r="D7" t="s">
         <v>25</v>
       </c>
@@ -618,6 +663,9 @@
       <c r="B8" t="s">
         <v>21</v>
       </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
@@ -638,6 +686,9 @@
       <c r="B9" t="s">
         <v>14</v>
       </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
       <c r="D9" t="s">
         <v>22</v>
       </c>
@@ -657,6 +708,9 @@
       </c>
       <c r="B10" t="s">
         <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E526EE6C-97AF-46FA-81B0-50C1C051EEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8147CA4-F776-44C7-B010-DE9F922313F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21255" yWindow="3210" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>check_group</t>
   </si>
@@ -101,45 +101,6 @@
   </si>
   <si>
     <t>num_children_under5,</t>
-  </si>
-  <si>
-    <t>sexratio</t>
-  </si>
-  <si>
-    <t>ageratio</t>
-  </si>
-  <si>
-    <t>anova</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 8</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>i</t>
   </si>
 </sst>
 </file>
@@ -484,7 +445,7 @@
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -525,21 +486,9 @@
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -548,21 +497,9 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -571,21 +508,9 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
       <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -594,21 +519,9 @@
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -617,21 +530,9 @@
       <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -640,21 +541,9 @@
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
       <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -663,21 +552,9 @@
       <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -686,21 +563,9 @@
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
       <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -709,20 +574,8 @@
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
       <c r="D10" t="s">
         <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8147CA4-F776-44C7-B010-DE9F922313F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC07E5B-7490-4F29-926A-BC49E76F73C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="93">
   <si>
     <t>check_group</t>
   </si>
@@ -64,12 +64,6 @@
     <t>Mean Deaths per Household</t>
   </si>
   <si>
-    <t>Mean Joiners per Household</t>
-  </si>
-  <si>
-    <t>Mean Leavers per Household</t>
-  </si>
-  <si>
     <t>num_male,num_female</t>
   </si>
   <si>
@@ -82,25 +76,229 @@
     <t>hh_size</t>
   </si>
   <si>
-    <t>Overall Mortality</t>
-  </si>
-  <si>
     <t>Mean Births per Household</t>
   </si>
   <si>
-    <t>num_join</t>
-  </si>
-  <si>
-    <t>num_left</t>
-  </si>
-  <si>
     <t>num_births</t>
   </si>
   <si>
     <t>num_died</t>
   </si>
   <si>
-    <t>num_children_under5,</t>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Spatial Distribution</t>
+  </si>
+  <si>
+    <t>Temporal Distribution</t>
+  </si>
+  <si>
+    <t>sexratio</t>
+  </si>
+  <si>
+    <t>ageratio</t>
+  </si>
+  <si>
+    <t>p_value &gt; 0.01 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.001 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &lt; 0.001</t>
+  </si>
+  <si>
+    <t>plaus_sex_ratio</t>
+  </si>
+  <si>
+    <t>num_children_under5,num_children_5_10yr</t>
+  </si>
+  <si>
+    <t>ttest</t>
+  </si>
+  <si>
+    <t>mu = 5</t>
+  </si>
+  <si>
+    <t>Demographic Representativeness</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_01_25</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_510</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_5plus</t>
+  </si>
+  <si>
+    <t>plaus_hhsize</t>
+  </si>
+  <si>
+    <t>plaus_deaths_per_hh</t>
+  </si>
+  <si>
+    <t>plaus_births_per_hh</t>
+  </si>
+  <si>
+    <t>poisson_ratio</t>
+  </si>
+  <si>
+    <t>expected_rate = 0.02</t>
+  </si>
+  <si>
+    <t>expected_rate = 0.075</t>
+  </si>
+  <si>
+    <t>index_dispersion</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.05</t>
+  </si>
+  <si>
+    <t>events_months_distribution</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.01 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &lt; 0.01</t>
+  </si>
+  <si>
+    <t>plaus_deaths_cluster_dist</t>
+  </si>
+  <si>
+    <t>plaus_deaths_month_dist</t>
+  </si>
+  <si>
+    <t>num_births, cluster</t>
+  </si>
+  <si>
+    <t>plaus_births_cluster_dist</t>
+  </si>
+  <si>
+    <t>Index Dispersion Deaths Across Clusters</t>
+  </si>
+  <si>
+    <t>Index Dispersion Births Across Clusters</t>
+  </si>
+  <si>
+    <t>Chi-Squared Test Deaths Across Months</t>
+  </si>
+  <si>
+    <t>num_births, month_of_birth</t>
+  </si>
+  <si>
+    <t>Enumerator Bias</t>
+  </si>
+  <si>
+    <t>Enumerator vs. Spatial</t>
+  </si>
+  <si>
+    <t>ANOVA - Deaths Reported per Enumerator/Team</t>
+  </si>
+  <si>
+    <t>ANOVA - Births Reported per Enumerator/Team</t>
+  </si>
+  <si>
+    <t>anova_by_exposure</t>
+  </si>
+  <si>
+    <t>plaus_deaths_enum_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_enum_dist</t>
+  </si>
+  <si>
+    <t>plaus_sex_ratio_enum</t>
+  </si>
+  <si>
+    <t>num_died, cluster</t>
+  </si>
+  <si>
+    <t>num_died, month_of_death</t>
+  </si>
+  <si>
+    <t>num_died, persontime, enum_id</t>
+  </si>
+  <si>
+    <t>num_births, persontime, enum_id</t>
+  </si>
+  <si>
+    <t>event_group_variance</t>
+  </si>
+  <si>
+    <t>plaus_deaths_enum_cluster_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_enum_months_dist</t>
+  </si>
+  <si>
+    <t>num_births, persontime, enum_id, cluster_id</t>
+  </si>
+  <si>
+    <t>num_died, persontime, enum_id, cluster_id</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Deaths for Enum and Clusters</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Births for Enum and Cluster</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_5plus_enum</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.3 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_statistic &gt;= 0.3 &amp; p_value &lt; 0.05 </t>
+  </si>
+  <si>
+    <t>Sex Ratio by Enumerator</t>
+  </si>
+  <si>
+    <t>Age Ratio 0-5 : 5 plus years by Enumerator</t>
+  </si>
+  <si>
+    <t>sexratio_count_group</t>
+  </si>
+  <si>
+    <t>ageratio_count_group</t>
+  </si>
+  <si>
+    <t>num_male,num_female, enum_id</t>
+  </si>
+  <si>
+    <t>num_children_under5, num_5plus, enum_id</t>
   </si>
 </sst>
 </file>
@@ -440,14 +638,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
     <col min="4" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -481,104 +679,1836 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>23</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E38" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" t="s">
+        <v>48</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" t="s">
+        <v>48</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" t="s">
+        <v>46</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
+      <c r="E46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50" t="s">
+        <v>47</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" t="s">
+        <v>90</v>
+      </c>
+      <c r="F53" t="s">
+        <v>29</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F54" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" t="s">
+        <v>62</v>
+      </c>
+      <c r="F55" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" t="s">
+        <v>62</v>
+      </c>
+      <c r="F56" t="s">
+        <v>48</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" t="s">
+        <v>49</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" t="s">
+        <v>62</v>
+      </c>
+      <c r="F60" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" t="s">
+        <v>49</v>
+      </c>
+      <c r="G61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F62" t="s">
+        <v>78</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63" t="s">
+        <v>70</v>
+      </c>
+      <c r="F63" t="s">
+        <v>80</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" t="s">
+        <v>70</v>
+      </c>
+      <c r="F64" t="s">
+        <v>79</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" t="s">
+        <v>74</v>
+      </c>
+      <c r="E65" t="s">
+        <v>70</v>
+      </c>
+      <c r="F65" t="s">
+        <v>81</v>
+      </c>
+      <c r="G65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" t="s">
+        <v>70</v>
+      </c>
+      <c r="F66" t="s">
+        <v>82</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" t="s">
+        <v>70</v>
+      </c>
+      <c r="F67" t="s">
+        <v>83</v>
+      </c>
+      <c r="G67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68" t="s">
+        <v>84</v>
+      </c>
+      <c r="G68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" t="s">
+        <v>75</v>
+      </c>
+      <c r="D69" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" t="s">
+        <v>74</v>
+      </c>
+      <c r="E70" t="s">
+        <v>70</v>
+      </c>
+      <c r="F70" t="s">
+        <v>86</v>
+      </c>
+      <c r="G70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71" t="s">
+        <v>73</v>
+      </c>
+      <c r="E71" t="s">
+        <v>70</v>
+      </c>
+      <c r="F71" t="s">
+        <v>78</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72" t="s">
+        <v>73</v>
+      </c>
+      <c r="E72" t="s">
+        <v>70</v>
+      </c>
+      <c r="F72" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" t="s">
+        <v>72</v>
+      </c>
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" t="s">
+        <v>70</v>
+      </c>
+      <c r="F73" t="s">
+        <v>79</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74" t="s">
+        <v>73</v>
+      </c>
+      <c r="E74" t="s">
+        <v>70</v>
+      </c>
+      <c r="F74" t="s">
+        <v>81</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" t="s">
+        <v>72</v>
+      </c>
+      <c r="C75" t="s">
+        <v>76</v>
+      </c>
+      <c r="D75" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" t="s">
+        <v>82</v>
+      </c>
+      <c r="G75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76" t="s">
+        <v>73</v>
+      </c>
+      <c r="E76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F76" t="s">
+        <v>83</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>59</v>
+      </c>
+      <c r="B77" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>73</v>
+      </c>
+      <c r="E77" t="s">
+        <v>70</v>
+      </c>
+      <c r="F77" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>59</v>
+      </c>
+      <c r="B78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78" t="s">
+        <v>73</v>
+      </c>
+      <c r="E78" t="s">
+        <v>70</v>
+      </c>
+      <c r="F78" t="s">
+        <v>85</v>
+      </c>
+      <c r="G78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" t="s">
+        <v>72</v>
+      </c>
+      <c r="C79" t="s">
+        <v>76</v>
+      </c>
+      <c r="D79" t="s">
+        <v>73</v>
+      </c>
+      <c r="E79" t="s">
+        <v>70</v>
+      </c>
+      <c r="F79" t="s">
+        <v>86</v>
+      </c>
+      <c r="G79">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC07E5B-7490-4F29-926A-BC49E76F73C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959187CB-E303-4CC1-A53B-81558F008E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -64,238 +64,238 @@
     <t>Mean Deaths per Household</t>
   </si>
   <si>
-    <t>num_male,num_female</t>
-  </si>
-  <si>
-    <t>num_children_2_5yr,num_5plus</t>
+    <t>hh_size</t>
+  </si>
+  <si>
+    <t>Mean Births per Household</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Spatial Distribution</t>
+  </si>
+  <si>
+    <t>Temporal Distribution</t>
+  </si>
+  <si>
+    <t>p_value &gt; 0.01 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.001 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &lt; 0.001</t>
+  </si>
+  <si>
+    <t>plaus_sex_ratio</t>
+  </si>
+  <si>
+    <t>ttest</t>
+  </si>
+  <si>
+    <t>mu = 5</t>
+  </si>
+  <si>
+    <t>Demographic Representativeness</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_01_25</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_510</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_5plus</t>
+  </si>
+  <si>
+    <t>plaus_hhsize</t>
+  </si>
+  <si>
+    <t>plaus_deaths_per_hh</t>
+  </si>
+  <si>
+    <t>plaus_births_per_hh</t>
+  </si>
+  <si>
+    <t>poisson_ratio</t>
+  </si>
+  <si>
+    <t>expected_rate = 0.02</t>
+  </si>
+  <si>
+    <t>expected_rate = 0.075</t>
+  </si>
+  <si>
+    <t>index_dispersion</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.05</t>
+  </si>
+  <si>
+    <t>events_months_distribution</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.01 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &lt; 0.01</t>
+  </si>
+  <si>
+    <t>plaus_deaths_cluster_dist</t>
+  </si>
+  <si>
+    <t>plaus_deaths_month_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_cluster_dist</t>
+  </si>
+  <si>
+    <t>Index Dispersion Deaths Across Clusters</t>
+  </si>
+  <si>
+    <t>Index Dispersion Births Across Clusters</t>
+  </si>
+  <si>
+    <t>Chi-Squared Test Deaths Across Months</t>
+  </si>
+  <si>
+    <t>num_births, month_of_birth</t>
+  </si>
+  <si>
+    <t>Enumerator Bias</t>
+  </si>
+  <si>
+    <t>Enumerator vs. Spatial</t>
+  </si>
+  <si>
+    <t>ANOVA - Deaths Reported per Enumerator/Team</t>
+  </si>
+  <si>
+    <t>ANOVA - Births Reported per Enumerator/Team</t>
+  </si>
+  <si>
+    <t>anova_by_exposure</t>
+  </si>
+  <si>
+    <t>plaus_deaths_enum_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_enum_dist</t>
+  </si>
+  <si>
+    <t>plaus_sex_ratio_enum</t>
+  </si>
+  <si>
+    <t>num_died, month_of_death</t>
+  </si>
+  <si>
+    <t>event_group_variance</t>
+  </si>
+  <si>
+    <t>plaus_deaths_enum_cluster_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_enum_months_dist</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Deaths for Enum and Clusters</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Births for Enum and Cluster</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_5plus_enum</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.3 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_statistic &gt;= 0.3 &amp; p_value &lt; 0.05 </t>
+  </si>
+  <si>
+    <t>Sex Ratio by Enumerator</t>
+  </si>
+  <si>
+    <t>Age Ratio 0-5 : 5 plus years by Enumerator</t>
+  </si>
+  <si>
+    <t>sexratio_count_group</t>
+  </si>
+  <si>
+    <t>ageratio_count_group</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time, enum_id</t>
+  </si>
+  <si>
+    <t>num_births, linked_person_time, enum_id</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time, enum_id, cluster_id</t>
+  </si>
+  <si>
+    <t>num_births, linked_person_time, enum_id, cluster_id</t>
+  </si>
+  <si>
+    <t>num_died, cluster_id</t>
+  </si>
+  <si>
+    <t>num_births, cluster_id</t>
+  </si>
+  <si>
+    <t>sexratio_count</t>
+  </si>
+  <si>
+    <t>ageratio_count</t>
+  </si>
+  <si>
+    <t>num_roster_male,num_roster_female</t>
+  </si>
+  <si>
+    <t>num_roster_male,num_roster_female, enum_id</t>
+  </si>
+  <si>
+    <t>num_children_under5,num_5_10yr</t>
+  </si>
+  <si>
+    <t>num_children_under2,num_children_2_5yr</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time</t>
+  </si>
+  <si>
+    <t>num_births, linked_person_time</t>
   </si>
   <si>
     <t>num_children_under5,num_5plus</t>
-  </si>
-  <si>
-    <t>hh_size</t>
-  </si>
-  <si>
-    <t>Mean Births per Household</t>
-  </si>
-  <si>
-    <t>num_births</t>
-  </si>
-  <si>
-    <t>num_died</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Spatial Distribution</t>
-  </si>
-  <si>
-    <t>Temporal Distribution</t>
-  </si>
-  <si>
-    <t>sexratio</t>
-  </si>
-  <si>
-    <t>ageratio</t>
-  </si>
-  <si>
-    <t>p_value &gt; 0.01 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.001 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>p_value &lt; 0.001</t>
-  </si>
-  <si>
-    <t>plaus_sex_ratio</t>
-  </si>
-  <si>
-    <t>num_children_under5,num_children_5_10yr</t>
-  </si>
-  <si>
-    <t>ttest</t>
-  </si>
-  <si>
-    <t>mu = 5</t>
-  </si>
-  <si>
-    <t>Demographic Representativeness</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_01_25</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_05_510</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_05_5plus</t>
-  </si>
-  <si>
-    <t>plaus_hhsize</t>
-  </si>
-  <si>
-    <t>plaus_deaths_per_hh</t>
-  </si>
-  <si>
-    <t>plaus_births_per_hh</t>
-  </si>
-  <si>
-    <t>poisson_ratio</t>
-  </si>
-  <si>
-    <t>expected_rate = 0.02</t>
-  </si>
-  <si>
-    <t>expected_rate = 0.075</t>
-  </si>
-  <si>
-    <t>index_dispersion</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.05</t>
-  </si>
-  <si>
-    <t>events_months_distribution</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.1</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.01 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>p_value &lt; 0.01</t>
-  </si>
-  <si>
-    <t>plaus_deaths_cluster_dist</t>
-  </si>
-  <si>
-    <t>plaus_deaths_month_dist</t>
-  </si>
-  <si>
-    <t>num_births, cluster</t>
-  </si>
-  <si>
-    <t>plaus_births_cluster_dist</t>
-  </si>
-  <si>
-    <t>Index Dispersion Deaths Across Clusters</t>
-  </si>
-  <si>
-    <t>Index Dispersion Births Across Clusters</t>
-  </si>
-  <si>
-    <t>Chi-Squared Test Deaths Across Months</t>
-  </si>
-  <si>
-    <t>num_births, month_of_birth</t>
-  </si>
-  <si>
-    <t>Enumerator Bias</t>
-  </si>
-  <si>
-    <t>Enumerator vs. Spatial</t>
-  </si>
-  <si>
-    <t>ANOVA - Deaths Reported per Enumerator/Team</t>
-  </si>
-  <si>
-    <t>ANOVA - Births Reported per Enumerator/Team</t>
-  </si>
-  <si>
-    <t>anova_by_exposure</t>
-  </si>
-  <si>
-    <t>plaus_deaths_enum_dist</t>
-  </si>
-  <si>
-    <t>plaus_births_enum_dist</t>
-  </si>
-  <si>
-    <t>plaus_sex_ratio_enum</t>
-  </si>
-  <si>
-    <t>num_died, cluster</t>
-  </si>
-  <si>
-    <t>num_died, month_of_death</t>
-  </si>
-  <si>
-    <t>num_died, persontime, enum_id</t>
-  </si>
-  <si>
-    <t>num_births, persontime, enum_id</t>
-  </si>
-  <si>
-    <t>event_group_variance</t>
-  </si>
-  <si>
-    <t>plaus_deaths_enum_cluster_dist</t>
-  </si>
-  <si>
-    <t>plaus_births_enum_months_dist</t>
-  </si>
-  <si>
-    <t>num_births, persontime, enum_id, cluster_id</t>
-  </si>
-  <si>
-    <t>num_died, persontime, enum_id, cluster_id</t>
-  </si>
-  <si>
-    <t>Likelihood Test Ratio - Deaths for Enum and Clusters</t>
-  </si>
-  <si>
-    <t>Likelihood Test Ratio - Births for Enum and Cluster</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_05_5plus_enum</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.10</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.3 &amp; p_value &gt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_statistic &gt;= 0.3 &amp; p_value &lt; 0.05 </t>
-  </si>
-  <si>
-    <t>Sex Ratio by Enumerator</t>
-  </si>
-  <si>
-    <t>Age Ratio 0-5 : 5 plus years by Enumerator</t>
-  </si>
-  <si>
-    <t>sexratio_count_group</t>
-  </si>
-  <si>
-    <t>ageratio_count_group</t>
-  </si>
-  <si>
-    <t>num_male,num_female, enum_id</t>
   </si>
   <si>
     <t>num_children_under5, num_5plus, enum_id</t>
@@ -305,7 +305,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,13 +313,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF001080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -334,8 +346,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,7 +660,7 @@
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
     <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" customWidth="1"/>
     <col min="5" max="5" width="33.85546875" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -679,22 +695,22 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
+        <v>85</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -702,22 +718,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
+        <v>85</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -725,22 +741,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
+        <v>85</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -748,22 +764,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -771,22 +787,22 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
+      <c r="D6" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -794,22 +810,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
-        <v>15</v>
+      <c r="D7" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -817,22 +833,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
+      <c r="D8" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -840,22 +856,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
-      <c r="D9" t="s">
-        <v>15</v>
+      <c r="D9" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -863,22 +879,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
+      <c r="D10" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -886,22 +902,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>31</v>
+      <c r="D11" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -909,22 +925,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
+      <c r="D12" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -932,22 +948,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
-        <v>31</v>
+      <c r="D13" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -955,22 +971,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -978,22 +994,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1001,22 +1017,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1024,22 +1040,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -1047,334 +1063,334 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" t="s">
-        <v>41</v>
+        <v>89</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
         <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" t="s">
-        <v>27</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
-        <v>41</v>
+        <v>89</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>41</v>
+        <v>89</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
         <v>21</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" t="s">
-        <v>28</v>
       </c>
       <c r="G28">
         <v>3</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1382,22 +1398,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1405,22 +1421,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G32">
         <v>3</v>
@@ -1428,22 +1444,22 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" t="s">
         <v>22</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" t="s">
-        <v>29</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -1451,22 +1467,22 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1474,22 +1490,22 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1497,22 +1513,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -1520,22 +1536,22 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" t="s">
         <v>22</v>
-      </c>
-      <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" t="s">
-        <v>29</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -1543,22 +1559,22 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1566,22 +1582,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E39" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -1589,22 +1605,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -1612,22 +1628,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -1635,22 +1651,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -1658,22 +1674,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -1681,22 +1697,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -1704,22 +1720,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" t="s">
-        <v>57</v>
+        <v>47</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G45">
         <v>5</v>
@@ -1727,22 +1743,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -1750,22 +1766,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E47" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -1773,22 +1789,22 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G48">
         <v>3</v>
@@ -1796,22 +1812,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E49" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F49" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -1819,22 +1835,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D50" t="s">
         <v>92</v>
       </c>
       <c r="E50" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -1842,22 +1858,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
         <v>92</v>
       </c>
       <c r="E51" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -1865,22 +1881,22 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D52" t="s">
         <v>92</v>
       </c>
       <c r="E52" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F52" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -1888,22 +1904,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D53" t="s">
         <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -1911,22 +1927,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -1934,22 +1950,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -1957,22 +1973,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D56" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E56" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -1980,22 +1996,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D57" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -2003,22 +2019,22 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D58" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2026,22 +2042,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D59" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2049,22 +2065,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D60" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -2072,22 +2088,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E61" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F61" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -2095,22 +2111,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" t="s">
         <v>59</v>
       </c>
-      <c r="B62" t="s">
-        <v>71</v>
-      </c>
       <c r="C62" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D62" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E62" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F62" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2118,22 +2134,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>50</v>
+      </c>
+      <c r="B63" t="s">
         <v>59</v>
       </c>
-      <c r="B63" t="s">
-        <v>71</v>
-      </c>
       <c r="C63" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E63" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F63" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2141,22 +2157,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" t="s">
         <v>59</v>
       </c>
-      <c r="B64" t="s">
-        <v>71</v>
-      </c>
       <c r="C64" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E64" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F64" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -2164,22 +2180,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" t="s">
         <v>59</v>
       </c>
-      <c r="B65" t="s">
-        <v>71</v>
-      </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F65" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2187,22 +2203,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66" t="s">
         <v>59</v>
       </c>
-      <c r="B66" t="s">
-        <v>71</v>
-      </c>
       <c r="C66" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E66" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F66" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -2210,22 +2226,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>50</v>
+      </c>
+      <c r="B67" t="s">
         <v>59</v>
       </c>
-      <c r="B67" t="s">
-        <v>71</v>
-      </c>
       <c r="C67" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E67" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F67" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G67">
         <v>5</v>
@@ -2233,22 +2249,22 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>50</v>
+      </c>
+      <c r="B68" t="s">
         <v>59</v>
       </c>
-      <c r="B68" t="s">
-        <v>71</v>
-      </c>
       <c r="C68" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E68" t="s">
+        <v>58</v>
+      </c>
+      <c r="F68" t="s">
         <v>70</v>
-      </c>
-      <c r="F68" t="s">
-        <v>84</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -2256,22 +2272,22 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" t="s">
         <v>59</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" t="s">
+        <v>58</v>
+      </c>
+      <c r="F69" t="s">
         <v>71</v>
-      </c>
-      <c r="C69" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" t="s">
-        <v>74</v>
-      </c>
-      <c r="E69" t="s">
-        <v>70</v>
-      </c>
-      <c r="F69" t="s">
-        <v>85</v>
       </c>
       <c r="G69">
         <v>7</v>
@@ -2279,22 +2295,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" t="s">
         <v>59</v>
       </c>
-      <c r="B70" t="s">
-        <v>71</v>
-      </c>
       <c r="C70" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E70" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F70" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G70">
         <v>8</v>
@@ -2302,22 +2318,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E71" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F71" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2325,22 +2341,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D72" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E72" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F72" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -2348,22 +2364,22 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E73" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F73" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2371,22 +2387,22 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E74" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F74" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -2394,22 +2410,22 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E75" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F75" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -2417,22 +2433,22 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E76" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F76" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -2440,22 +2456,22 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E77" t="s">
+        <v>58</v>
+      </c>
+      <c r="F77" t="s">
         <v>70</v>
-      </c>
-      <c r="F77" t="s">
-        <v>84</v>
       </c>
       <c r="G77">
         <v>6</v>
@@ -2463,22 +2479,22 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E78" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F78" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -2486,22 +2502,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B79" t="s">
+        <v>60</v>
+      </c>
+      <c r="C79" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" t="s">
+        <v>80</v>
+      </c>
+      <c r="E79" t="s">
+        <v>58</v>
+      </c>
+      <c r="F79" t="s">
         <v>72</v>
-      </c>
-      <c r="C79" t="s">
-        <v>76</v>
-      </c>
-      <c r="D79" t="s">
-        <v>73</v>
-      </c>
-      <c r="E79" t="s">
-        <v>70</v>
-      </c>
-      <c r="F79" t="s">
-        <v>86</v>
       </c>
       <c r="G79">
         <v>8</v>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959187CB-E303-4CC1-A53B-81558F008E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62CB0AF-56EA-4D07-8FAF-558C668AFCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="96">
   <si>
     <t>check_group</t>
   </si>
@@ -166,9 +166,6 @@
     <t>Chi-Squared Test Deaths Across Months</t>
   </si>
   <si>
-    <t>num_births, month_of_birth</t>
-  </si>
-  <si>
     <t>Enumerator Bias</t>
   </si>
   <si>
@@ -193,9 +190,6 @@
     <t>plaus_sex_ratio_enum</t>
   </si>
   <si>
-    <t>num_died, month_of_death</t>
-  </si>
-  <si>
     <t>event_group_variance</t>
   </si>
   <si>
@@ -299,6 +293,21 @@
   </si>
   <si>
     <t>num_children_under5, num_5plus, enum_id</t>
+  </si>
+  <si>
+    <t>num_died, linked_death_months</t>
+  </si>
+  <si>
+    <t>num_births, linked_birth_months</t>
+  </si>
+  <si>
+    <t>expected_ratio = c(0.4118, 0.5882)</t>
+  </si>
+  <si>
+    <t>expected_ratio = c(0.5238, 0.4762)</t>
+  </si>
+  <si>
+    <t>expected_ratio = c(.2,.8)</t>
   </si>
 </sst>
 </file>
@@ -704,10 +713,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
@@ -727,10 +736,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -750,10 +759,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -773,10 +782,10 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
@@ -796,16 +805,19 @@
         <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6">
         <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -819,16 +831,19 @@
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
       </c>
       <c r="G7">
         <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -842,16 +857,19 @@
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
       </c>
       <c r="G8">
         <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -865,16 +883,19 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9">
         <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -888,16 +909,19 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
         <v>39</v>
       </c>
       <c r="G10">
         <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -911,16 +935,19 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
       </c>
       <c r="G11">
         <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -934,16 +961,19 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
       </c>
       <c r="G12">
         <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -957,16 +987,19 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13">
         <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -980,16 +1013,19 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
       </c>
       <c r="G14">
         <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,16 +1039,19 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15">
         <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1026,16 +1065,19 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
       </c>
       <c r="G16">
         <v>3</v>
+      </c>
+      <c r="H16" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1049,16 +1091,19 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
       </c>
       <c r="G17">
         <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1176,7 +1221,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>33</v>
@@ -1202,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>33</v>
@@ -1228,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>33</v>
@@ -1254,7 +1299,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>33</v>
@@ -1280,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>33</v>
@@ -1306,7 +1351,7 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>33</v>
@@ -1332,7 +1377,7 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>33</v>
@@ -1358,7 +1403,7 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>33</v>
@@ -1384,7 +1429,7 @@
         <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
         <v>36</v>
@@ -1407,7 +1452,7 @@
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s">
         <v>36</v>
@@ -1430,7 +1475,7 @@
         <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E32" t="s">
         <v>36</v>
@@ -1453,7 +1498,7 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s">
         <v>36</v>
@@ -1476,7 +1521,7 @@
         <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
@@ -1499,7 +1544,7 @@
         <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -1522,7 +1567,7 @@
         <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -1545,7 +1590,7 @@
         <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
@@ -1568,7 +1613,7 @@
         <v>47</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
         <v>38</v>
@@ -1591,7 +1636,7 @@
         <v>47</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -1614,7 +1659,7 @@
         <v>47</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -1637,7 +1682,7 @@
         <v>47</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E41" t="s">
         <v>38</v>
@@ -1660,7 +1705,7 @@
         <v>47</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
@@ -1683,7 +1728,7 @@
         <v>47</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
         <v>38</v>
@@ -1706,7 +1751,7 @@
         <v>47</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
         <v>38</v>
@@ -1729,7 +1774,7 @@
         <v>47</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -1743,19 +1788,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" t="s">
         <v>73</v>
-      </c>
-      <c r="D46" t="s">
-        <v>86</v>
-      </c>
-      <c r="E46" t="s">
-        <v>75</v>
       </c>
       <c r="F46" t="s">
         <v>39</v>
@@ -1766,19 +1811,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" t="s">
         <v>73</v>
-      </c>
-      <c r="D47" t="s">
-        <v>86</v>
-      </c>
-      <c r="E47" t="s">
-        <v>75</v>
       </c>
       <c r="F47" t="s">
         <v>20</v>
@@ -1789,19 +1834,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" t="s">
         <v>73</v>
-      </c>
-      <c r="D48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E48" t="s">
-        <v>75</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -1812,19 +1857,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
+        <v>71</v>
+      </c>
+      <c r="D49" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" t="s">
         <v>73</v>
-      </c>
-      <c r="D49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49" t="s">
-        <v>75</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
@@ -1835,19 +1880,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
         <v>74</v>
-      </c>
-      <c r="D50" t="s">
-        <v>92</v>
-      </c>
-      <c r="E50" t="s">
-        <v>76</v>
       </c>
       <c r="F50" t="s">
         <v>39</v>
@@ -1858,19 +1903,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" t="s">
         <v>74</v>
-      </c>
-      <c r="D51" t="s">
-        <v>92</v>
-      </c>
-      <c r="E51" t="s">
-        <v>76</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -1881,19 +1926,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
         <v>74</v>
-      </c>
-      <c r="D52" t="s">
-        <v>92</v>
-      </c>
-      <c r="E52" t="s">
-        <v>76</v>
       </c>
       <c r="F52" t="s">
         <v>21</v>
@@ -1904,19 +1949,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" t="s">
+        <v>90</v>
+      </c>
+      <c r="E53" t="s">
         <v>74</v>
-      </c>
-      <c r="D53" t="s">
-        <v>92</v>
-      </c>
-      <c r="E53" t="s">
-        <v>76</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
@@ -1927,19 +1972,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F54" t="s">
         <v>39</v>
@@ -1950,19 +1995,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F55" t="s">
         <v>20</v>
@@ -1973,19 +2018,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F56" t="s">
         <v>40</v>
@@ -1996,19 +2041,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F57" t="s">
         <v>41</v>
@@ -2019,19 +2064,19 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" t="s">
         <v>52</v>
-      </c>
-      <c r="D58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" t="s">
-        <v>53</v>
       </c>
       <c r="F58" t="s">
         <v>39</v>
@@ -2042,19 +2087,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" t="s">
         <v>52</v>
-      </c>
-      <c r="D59" t="s">
-        <v>78</v>
-      </c>
-      <c r="E59" t="s">
-        <v>53</v>
       </c>
       <c r="F59" t="s">
         <v>20</v>
@@ -2065,19 +2110,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" t="s">
         <v>52</v>
-      </c>
-      <c r="D60" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" t="s">
-        <v>53</v>
       </c>
       <c r="F60" t="s">
         <v>40</v>
@@ -2088,19 +2133,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" t="s">
         <v>52</v>
-      </c>
-      <c r="D61" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" t="s">
-        <v>53</v>
       </c>
       <c r="F61" t="s">
         <v>41</v>
@@ -2111,22 +2156,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C62" t="s">
         <v>59</v>
       </c>
-      <c r="C62" t="s">
-        <v>61</v>
-      </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E62" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F62" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2134,22 +2179,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" t="s">
         <v>59</v>
       </c>
-      <c r="C63" t="s">
-        <v>61</v>
-      </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E63" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F63" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2157,22 +2202,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C64" t="s">
         <v>59</v>
       </c>
-      <c r="C64" t="s">
-        <v>61</v>
-      </c>
       <c r="D64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F64" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -2180,22 +2225,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65" t="s">
         <v>59</v>
       </c>
-      <c r="C65" t="s">
-        <v>61</v>
-      </c>
       <c r="D65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E65" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2203,22 +2248,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" t="s">
         <v>59</v>
       </c>
-      <c r="C66" t="s">
-        <v>61</v>
-      </c>
       <c r="D66" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E66" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -2226,22 +2271,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" t="s">
         <v>59</v>
       </c>
-      <c r="C67" t="s">
-        <v>61</v>
-      </c>
       <c r="D67" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F67" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G67">
         <v>5</v>
@@ -2249,22 +2294,22 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" t="s">
         <v>59</v>
       </c>
-      <c r="C68" t="s">
-        <v>61</v>
-      </c>
       <c r="D68" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E68" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -2272,22 +2317,22 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B69" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" t="s">
         <v>59</v>
       </c>
-      <c r="C69" t="s">
-        <v>61</v>
-      </c>
       <c r="D69" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F69" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G69">
         <v>7</v>
@@ -2295,22 +2340,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" t="s">
         <v>59</v>
       </c>
-      <c r="C70" t="s">
-        <v>61</v>
-      </c>
       <c r="D70" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E70" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F70" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G70">
         <v>8</v>
@@ -2318,22 +2363,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B71" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" t="s">
         <v>60</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71" t="s">
         <v>62</v>
-      </c>
-      <c r="D71" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71" t="s">
-        <v>58</v>
-      </c>
-      <c r="F71" t="s">
-        <v>64</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2341,22 +2386,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
         <v>60</v>
       </c>
-      <c r="C72" t="s">
-        <v>62</v>
-      </c>
       <c r="D72" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E72" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -2364,22 +2409,22 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" t="s">
         <v>60</v>
       </c>
-      <c r="C73" t="s">
-        <v>62</v>
-      </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E73" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F73" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2387,22 +2432,22 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B74" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" t="s">
         <v>60</v>
       </c>
-      <c r="C74" t="s">
-        <v>62</v>
-      </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E74" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F74" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -2410,22 +2455,22 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
         <v>60</v>
       </c>
-      <c r="C75" t="s">
-        <v>62</v>
-      </c>
       <c r="D75" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E75" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F75" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -2433,22 +2478,22 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" t="s">
         <v>60</v>
       </c>
-      <c r="C76" t="s">
-        <v>62</v>
-      </c>
       <c r="D76" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F76" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -2456,22 +2501,22 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B77" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" t="s">
         <v>60</v>
       </c>
-      <c r="C77" t="s">
-        <v>62</v>
-      </c>
       <c r="D77" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E77" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G77">
         <v>6</v>
@@ -2479,22 +2524,22 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B78" t="s">
+        <v>58</v>
+      </c>
+      <c r="C78" t="s">
         <v>60</v>
       </c>
-      <c r="C78" t="s">
-        <v>62</v>
-      </c>
       <c r="D78" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E78" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F78" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -2502,22 +2547,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" t="s">
         <v>60</v>
       </c>
-      <c r="C79" t="s">
-        <v>62</v>
-      </c>
       <c r="D79" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E79" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F79" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G79">
         <v>8</v>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62CB0AF-56EA-4D07-8FAF-558C668AFCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B95E5B-AF5A-43A6-882E-937EBAB2AE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-345" yWindow="10575" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B95E5B-AF5A-43A6-882E-937EBAB2AE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7F321A-EE3C-47C2-AFC3-5184E8CF59B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-345" yWindow="10575" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-345" yWindow="4185" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -97,217 +97,217 @@
     <t>ttest</t>
   </si>
   <si>
+    <t>Demographic Representativeness</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_01_25</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_510</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_5plus</t>
+  </si>
+  <si>
+    <t>plaus_hhsize</t>
+  </si>
+  <si>
+    <t>plaus_deaths_per_hh</t>
+  </si>
+  <si>
+    <t>plaus_births_per_hh</t>
+  </si>
+  <si>
+    <t>poisson_ratio</t>
+  </si>
+  <si>
+    <t>expected_rate = 0.02</t>
+  </si>
+  <si>
+    <t>expected_rate = 0.075</t>
+  </si>
+  <si>
+    <t>index_dispersion</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.05</t>
+  </si>
+  <si>
+    <t>events_months_distribution</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.1</t>
+  </si>
+  <si>
+    <t>p_value &gt;= 0.01 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>p_value &lt; 0.01</t>
+  </si>
+  <si>
+    <t>plaus_deaths_cluster_dist</t>
+  </si>
+  <si>
+    <t>plaus_deaths_month_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_cluster_dist</t>
+  </si>
+  <si>
+    <t>Index Dispersion Deaths Across Clusters</t>
+  </si>
+  <si>
+    <t>Index Dispersion Births Across Clusters</t>
+  </si>
+  <si>
+    <t>Chi-Squared Test Deaths Across Months</t>
+  </si>
+  <si>
+    <t>Enumerator Bias</t>
+  </si>
+  <si>
+    <t>Enumerator vs. Spatial</t>
+  </si>
+  <si>
+    <t>ANOVA - Deaths Reported per Enumerator/Team</t>
+  </si>
+  <si>
+    <t>ANOVA - Births Reported per Enumerator/Team</t>
+  </si>
+  <si>
+    <t>anova_by_exposure</t>
+  </si>
+  <si>
+    <t>plaus_deaths_enum_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_enum_dist</t>
+  </si>
+  <si>
+    <t>plaus_sex_ratio_enum</t>
+  </si>
+  <si>
+    <t>event_group_variance</t>
+  </si>
+  <si>
+    <t>plaus_deaths_enum_cluster_dist</t>
+  </si>
+  <si>
+    <t>plaus_births_enum_months_dist</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Deaths for Enum and Clusters</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Births for Enum and Cluster</t>
+  </si>
+  <si>
+    <t>plaus_ageratio_05_5plus_enum</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.3 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_statistic &gt;= 0.3 &amp; p_value &lt; 0.05 </t>
+  </si>
+  <si>
+    <t>Sex Ratio by Enumerator</t>
+  </si>
+  <si>
+    <t>Age Ratio 0-5 : 5 plus years by Enumerator</t>
+  </si>
+  <si>
+    <t>sexratio_count_group</t>
+  </si>
+  <si>
+    <t>ageratio_count_group</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time, enum_id</t>
+  </si>
+  <si>
+    <t>num_births, linked_person_time, enum_id</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time, enum_id, cluster_id</t>
+  </si>
+  <si>
+    <t>num_births, linked_person_time, enum_id, cluster_id</t>
+  </si>
+  <si>
+    <t>num_died, cluster_id</t>
+  </si>
+  <si>
+    <t>num_births, cluster_id</t>
+  </si>
+  <si>
+    <t>sexratio_count</t>
+  </si>
+  <si>
+    <t>ageratio_count</t>
+  </si>
+  <si>
+    <t>num_roster_male,num_roster_female</t>
+  </si>
+  <si>
+    <t>num_roster_male,num_roster_female, enum_id</t>
+  </si>
+  <si>
+    <t>num_children_under5,num_5_10yr</t>
+  </si>
+  <si>
+    <t>num_children_under2,num_children_2_5yr</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time</t>
+  </si>
+  <si>
+    <t>num_births, linked_person_time</t>
+  </si>
+  <si>
+    <t>num_children_under5,num_5plus</t>
+  </si>
+  <si>
+    <t>num_children_under5, num_5plus, enum_id</t>
+  </si>
+  <si>
+    <t>num_died, linked_death_months</t>
+  </si>
+  <si>
+    <t>num_births, linked_birth_months</t>
+  </si>
+  <si>
+    <t>expected_ratio = c(0.4118, 0.5882)</t>
+  </si>
+  <si>
+    <t>expected_ratio = c(0.5238, 0.4762)</t>
+  </si>
+  <si>
+    <t>expected_ratio = c(.2,.8)</t>
+  </si>
+  <si>
     <t>mu = 5</t>
-  </si>
-  <si>
-    <t>Demographic Representativeness</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_01_25</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_05_510</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_05_5plus</t>
-  </si>
-  <si>
-    <t>plaus_hhsize</t>
-  </si>
-  <si>
-    <t>plaus_deaths_per_hh</t>
-  </si>
-  <si>
-    <t>plaus_births_per_hh</t>
-  </si>
-  <si>
-    <t>poisson_ratio</t>
-  </si>
-  <si>
-    <t>expected_rate = 0.02</t>
-  </si>
-  <si>
-    <t>expected_rate = 0.075</t>
-  </si>
-  <si>
-    <t>index_dispersion</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.05</t>
-  </si>
-  <si>
-    <t>events_months_distribution</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.1</t>
-  </si>
-  <si>
-    <t>p_value &gt;= 0.01 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>p_value &lt; 0.01</t>
-  </si>
-  <si>
-    <t>plaus_deaths_cluster_dist</t>
-  </si>
-  <si>
-    <t>plaus_deaths_month_dist</t>
-  </si>
-  <si>
-    <t>plaus_births_cluster_dist</t>
-  </si>
-  <si>
-    <t>Index Dispersion Deaths Across Clusters</t>
-  </si>
-  <si>
-    <t>Index Dispersion Births Across Clusters</t>
-  </si>
-  <si>
-    <t>Chi-Squared Test Deaths Across Months</t>
-  </si>
-  <si>
-    <t>Enumerator Bias</t>
-  </si>
-  <si>
-    <t>Enumerator vs. Spatial</t>
-  </si>
-  <si>
-    <t>ANOVA - Deaths Reported per Enumerator/Team</t>
-  </si>
-  <si>
-    <t>ANOVA - Births Reported per Enumerator/Team</t>
-  </si>
-  <si>
-    <t>anova_by_exposure</t>
-  </si>
-  <si>
-    <t>plaus_deaths_enum_dist</t>
-  </si>
-  <si>
-    <t>plaus_births_enum_dist</t>
-  </si>
-  <si>
-    <t>plaus_sex_ratio_enum</t>
-  </si>
-  <si>
-    <t>event_group_variance</t>
-  </si>
-  <si>
-    <t>plaus_deaths_enum_cluster_dist</t>
-  </si>
-  <si>
-    <t>plaus_births_enum_months_dist</t>
-  </si>
-  <si>
-    <t>Likelihood Test Ratio - Deaths for Enum and Clusters</t>
-  </si>
-  <si>
-    <t>Likelihood Test Ratio - Births for Enum and Cluster</t>
-  </si>
-  <si>
-    <t>plaus_ageratio_05_5plus_enum</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.10</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.3 &amp; p_value &gt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_statistic &gt;= 0.3 &amp; p_value &lt; 0.05 </t>
-  </si>
-  <si>
-    <t>Sex Ratio by Enumerator</t>
-  </si>
-  <si>
-    <t>Age Ratio 0-5 : 5 plus years by Enumerator</t>
-  </si>
-  <si>
-    <t>sexratio_count_group</t>
-  </si>
-  <si>
-    <t>ageratio_count_group</t>
-  </si>
-  <si>
-    <t>num_died, linked_person_time, enum_id</t>
-  </si>
-  <si>
-    <t>num_births, linked_person_time, enum_id</t>
-  </si>
-  <si>
-    <t>num_died, linked_person_time, enum_id, cluster_id</t>
-  </si>
-  <si>
-    <t>num_births, linked_person_time, enum_id, cluster_id</t>
-  </si>
-  <si>
-    <t>num_died, cluster_id</t>
-  </si>
-  <si>
-    <t>num_births, cluster_id</t>
-  </si>
-  <si>
-    <t>sexratio_count</t>
-  </si>
-  <si>
-    <t>ageratio_count</t>
-  </si>
-  <si>
-    <t>num_roster_male,num_roster_female</t>
-  </si>
-  <si>
-    <t>num_roster_male,num_roster_female, enum_id</t>
-  </si>
-  <si>
-    <t>num_children_under5,num_5_10yr</t>
-  </si>
-  <si>
-    <t>num_children_under2,num_children_2_5yr</t>
-  </si>
-  <si>
-    <t>num_died, linked_person_time</t>
-  </si>
-  <si>
-    <t>num_births, linked_person_time</t>
-  </si>
-  <si>
-    <t>num_children_under5,num_5plus</t>
-  </si>
-  <si>
-    <t>num_children_under5, num_5plus, enum_id</t>
-  </si>
-  <si>
-    <t>num_died, linked_death_months</t>
-  </si>
-  <si>
-    <t>num_births, linked_birth_months</t>
-  </si>
-  <si>
-    <t>expected_ratio = c(0.4118, 0.5882)</t>
-  </si>
-  <si>
-    <t>expected_ratio = c(0.5238, 0.4762)</t>
-  </si>
-  <si>
-    <t>expected_ratio = c(.2,.8)</t>
   </si>
 </sst>
 </file>
@@ -704,7 +704,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
@@ -713,13 +713,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -727,7 +727,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -736,10 +736,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -759,10 +759,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -782,10 +782,10 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
@@ -796,45 +796,45 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -843,24 +843,24 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -869,24 +869,24 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -895,50 +895,50 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -947,24 +947,24 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -973,24 +973,24 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
@@ -999,50 +999,50 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -1051,24 +1051,24 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1077,24 +1077,24 @@
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1103,15 +1103,15 @@
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1123,21 +1123,21 @@
         <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1155,15 +1155,15 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1181,15 +1181,15 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1207,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,25 +1215,25 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,16 +1241,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
         <v>20</v>
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,16 +1267,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -1285,7 +1285,7 @@
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,16 +1293,16 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
@@ -1311,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,25 +1319,25 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,16 +1345,16 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1363,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,16 +1371,16 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -1389,7 +1389,7 @@
         <v>3</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,16 +1397,16 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>22</v>
@@ -1415,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,19 +1423,19 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" t="s">
         <v>36</v>
-      </c>
-      <c r="F30" t="s">
-        <v>37</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1446,16 +1446,16 @@
         <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" t="s">
         <v>19</v>
@@ -1469,16 +1469,16 @@
         <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -1492,16 +1492,16 @@
         <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
@@ -1515,19 +1515,19 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E34" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" t="s">
         <v>36</v>
-      </c>
-      <c r="F34" t="s">
-        <v>37</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1538,16 +1538,16 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
@@ -1561,16 +1561,16 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -1584,16 +1584,16 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F37" t="s">
         <v>22</v>
@@ -1607,19 +1607,19 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" t="s">
         <v>38</v>
-      </c>
-      <c r="F38" t="s">
-        <v>39</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1630,16 +1630,16 @@
         <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
         <v>20</v>
@@ -1653,19 +1653,19 @@
         <v>18</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G40">
         <v>3</v>
@@ -1676,19 +1676,19 @@
         <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -1699,19 +1699,19 @@
         <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" t="s">
         <v>38</v>
-      </c>
-      <c r="F42" t="s">
-        <v>39</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -1722,16 +1722,16 @@
         <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
         <v>20</v>
@@ -1745,19 +1745,19 @@
         <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -1768,19 +1768,19 @@
         <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G45">
         <v>5</v>
@@ -1788,22 +1788,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -1811,19 +1811,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F47" t="s">
         <v>20</v>
@@ -1834,19 +1834,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -1857,19 +1857,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
@@ -1880,22 +1880,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -1903,19 +1903,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -1926,19 +1926,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F52" t="s">
         <v>21</v>
@@ -1949,19 +1949,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
@@ -1972,22 +1972,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -1995,19 +1995,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
         <v>20</v>
@@ -2018,22 +2018,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -2064,22 +2064,22 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
+        <v>50</v>
+      </c>
+      <c r="D58" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" t="s">
         <v>51</v>
       </c>
-      <c r="D58" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" t="s">
-        <v>52</v>
-      </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2087,19 +2087,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
+        <v>50</v>
+      </c>
+      <c r="D59" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" t="s">
         <v>51</v>
-      </c>
-      <c r="D59" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" t="s">
-        <v>52</v>
       </c>
       <c r="F59" t="s">
         <v>20</v>
@@ -2110,22 +2110,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" t="s">
         <v>51</v>
       </c>
-      <c r="D60" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" t="s">
-        <v>52</v>
-      </c>
       <c r="F60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G60">
         <v>3</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
+        <v>50</v>
+      </c>
+      <c r="D61" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" t="s">
         <v>51</v>
       </c>
-      <c r="D61" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" t="s">
-        <v>52</v>
-      </c>
       <c r="F61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -2156,22 +2156,22 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2179,22 +2179,22 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -2225,22 +2225,22 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2248,22 +2248,22 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E66" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -2271,22 +2271,22 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E67" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G67">
         <v>5</v>
@@ -2294,22 +2294,22 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G69">
         <v>7</v>
@@ -2340,22 +2340,22 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E70" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G70">
         <v>8</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B71" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E71" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2386,22 +2386,22 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2432,22 +2432,22 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B74" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E74" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -2455,22 +2455,22 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -2478,22 +2478,22 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C76" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E76" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -2501,22 +2501,22 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E77" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G77">
         <v>6</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E78" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -2547,22 +2547,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C79" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E79" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F79" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G79">
         <v>8</v>

--- a/inst/resources/quality_schema_data_quality_mortality_template.xlsx
+++ b/inst/resources/quality_schema_data_quality_mortality_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7F321A-EE3C-47C2-AFC3-5184E8CF59B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E261D4-45FE-4490-8710-AA3A688D31DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-345" yWindow="4185" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality Checks" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="99">
   <si>
     <t>check_group</t>
   </si>
@@ -193,45 +193,12 @@
     <t>plaus_deaths_enum_cluster_dist</t>
   </si>
   <si>
-    <t>plaus_births_enum_months_dist</t>
-  </si>
-  <si>
-    <t>Likelihood Test Ratio - Deaths for Enum and Clusters</t>
-  </si>
-  <si>
     <t>Likelihood Test Ratio - Births for Enum and Cluster</t>
   </si>
   <si>
     <t>plaus_ageratio_05_5plus_enum</t>
   </si>
   <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.10</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>test_statistic &lt; 0.1 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.1 &amp; test_statistic &lt; 0.3 &amp; p_value &lt; 0.05</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.3 &amp; p_value &gt; 0.1</t>
-  </si>
-  <si>
-    <t>test_statistic &gt;= 0.3 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_statistic &gt;= 0.3 &amp; p_value &lt; 0.05 </t>
-  </si>
-  <si>
     <t>Sex Ratio by Enumerator</t>
   </si>
   <si>
@@ -308,13 +275,55 @@
   </si>
   <si>
     <t>mu = 5</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 10 &amp; p_value &gt;= 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 10 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.10</t>
+  </si>
+  <si>
+    <t>test_statistic &lt; 10 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 10 &amp; test_statistic &lt; 30 &amp; p_value &lt; 0.05</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 10 &amp; test_statistic &lt; 30 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 10 &amp; test_statistic &lt; 30 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 30 &amp; p_value &gt; 0.1</t>
+  </si>
+  <si>
+    <t>test_statistic &gt;= 30 &amp; p_value &gt;= 0.05 &amp; p_value &lt; 0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test_statistic &gt;= 30 &amp; p_value &lt; 0.05 </t>
+  </si>
+  <si>
+    <t>plaus_births_enum_cluster_dist</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Percent Variance from Enumerators (control clusters)</t>
+  </si>
+  <si>
+    <t>plaus_deaths_cluster_enum_dist</t>
+  </si>
+  <si>
+    <t>Likelihood Test Ratio - Percent Variance From Clusters (control enum)</t>
+  </si>
+  <si>
+    <t>num_died, linked_person_time, cluster_id, enum_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +336,12 @@
       <color rgb="FF001080"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -355,11 +370,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -663,15 +684,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="82.140625" customWidth="1"/>
     <col min="4" max="4" width="57.5703125" customWidth="1"/>
     <col min="5" max="5" width="33.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="75.85546875" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -713,10 +734,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F2" t="s">
         <v>38</v>
@@ -736,10 +757,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -759,10 +780,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -782,10 +803,10 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
@@ -805,10 +826,10 @@
         <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
         <v>38</v>
@@ -817,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -831,10 +852,10 @@
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -843,7 +864,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -857,10 +878,10 @@
         <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -869,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -883,10 +904,10 @@
         <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -895,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -909,10 +930,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F10" t="s">
         <v>38</v>
@@ -921,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -935,10 +956,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
         <v>20</v>
@@ -947,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -961,10 +982,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -973,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -987,10 +1008,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
@@ -999,7 +1020,7 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1013,10 +1034,10 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
         <v>38</v>
@@ -1025,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1039,10 +1060,10 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
@@ -1051,7 +1072,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1065,10 +1086,10 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1077,7 +1098,7 @@
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1091,10 +1112,10 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1103,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1129,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1155,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1181,7 +1202,7 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1207,7 +1228,7 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1221,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>32</v>
@@ -1247,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>32</v>
@@ -1273,7 +1294,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>32</v>
@@ -1299,7 +1320,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>32</v>
@@ -1325,7 +1346,7 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>32</v>
@@ -1351,7 +1372,7 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>32</v>
@@ -1377,7 +1398,7 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>32</v>
@@ -1403,7 +1424,7 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>32</v>
@@ -1429,7 +1450,7 @@
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
         <v>35</v>
@@ -1452,7 +1473,7 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
         <v>35</v>
@@ -1475,7 +1496,7 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s">
         <v>35</v>
@@ -1498,7 +1519,7 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
         <v>35</v>
@@ -1521,7 +1542,7 @@
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
         <v>35</v>
@@ -1544,7 +1565,7 @@
         <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E35" t="s">
         <v>35</v>
@@ -1567,7 +1588,7 @@
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E36" t="s">
         <v>35</v>
@@ -1590,7 +1611,7 @@
         <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E37" t="s">
         <v>35</v>
@@ -1613,7 +1634,7 @@
         <v>46</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
         <v>37</v>
@@ -1636,7 +1657,7 @@
         <v>46</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E39" t="s">
         <v>37</v>
@@ -1659,7 +1680,7 @@
         <v>46</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
         <v>37</v>
@@ -1682,7 +1703,7 @@
         <v>46</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E41" t="s">
         <v>37</v>
@@ -1705,7 +1726,7 @@
         <v>46</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E42" t="s">
         <v>37</v>
@@ -1728,7 +1749,7 @@
         <v>46</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E43" t="s">
         <v>37</v>
@@ -1751,7 +1772,7 @@
         <v>46</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E44" t="s">
         <v>37</v>
@@ -1774,7 +1795,7 @@
         <v>46</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E45" t="s">
         <v>37</v>
@@ -1794,13 +1815,13 @@
         <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F46" t="s">
         <v>38</v>
@@ -1817,13 +1838,13 @@
         <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F47" t="s">
         <v>20</v>
@@ -1840,13 +1861,13 @@
         <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D48" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -1863,13 +1884,13 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
@@ -1883,16 +1904,16 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
         <v>60</v>
       </c>
-      <c r="C50" t="s">
-        <v>71</v>
-      </c>
       <c r="D50" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F50" t="s">
         <v>38</v>
@@ -1906,16 +1927,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
         <v>60</v>
       </c>
-      <c r="C51" t="s">
-        <v>71</v>
-      </c>
       <c r="D51" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F51" t="s">
         <v>20</v>
@@ -1929,16 +1950,16 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
         <v>60</v>
       </c>
-      <c r="C52" t="s">
-        <v>71</v>
-      </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F52" t="s">
         <v>21</v>
@@ -1952,16 +1973,16 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
         <v>60</v>
       </c>
-      <c r="C53" t="s">
-        <v>71</v>
-      </c>
       <c r="D53" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E53" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
@@ -1981,7 +2002,7 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E54" t="s">
         <v>51</v>
@@ -2004,7 +2025,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E55" t="s">
         <v>51</v>
@@ -2027,7 +2048,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E56" t="s">
         <v>51</v>
@@ -2050,7 +2071,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E57" t="s">
         <v>51</v>
@@ -2073,7 +2094,7 @@
         <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E58" t="s">
         <v>51</v>
@@ -2096,7 +2117,7 @@
         <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E59" t="s">
         <v>51</v>
@@ -2119,7 +2140,7 @@
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E60" t="s">
         <v>51</v>
@@ -2142,7 +2163,7 @@
         <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E61" t="s">
         <v>51</v>
@@ -2162,16 +2183,16 @@
         <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E62" t="s">
         <v>55</v>
       </c>
       <c r="F62" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2185,16 +2206,16 @@
         <v>56</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D63" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E63" t="s">
         <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2208,16 +2229,16 @@
         <v>56</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D64" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E64" t="s">
         <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="G64">
         <v>2</v>
@@ -2231,16 +2252,16 @@
         <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E65" t="s">
         <v>55</v>
       </c>
       <c r="F65" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -2254,16 +2275,16 @@
         <v>56</v>
       </c>
       <c r="C66" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E66" t="s">
         <v>55</v>
       </c>
       <c r="F66" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G66">
         <v>4</v>
@@ -2277,16 +2298,16 @@
         <v>56</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E67" t="s">
         <v>55</v>
       </c>
       <c r="F67" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G67">
         <v>5</v>
@@ -2300,16 +2321,16 @@
         <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E68" t="s">
         <v>55</v>
       </c>
       <c r="F68" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -2323,16 +2344,16 @@
         <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E69" t="s">
         <v>55</v>
       </c>
       <c r="F69" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G69">
         <v>7</v>
@@ -2346,16 +2367,16 @@
         <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E70" t="s">
         <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G70">
         <v>8</v>
@@ -2366,19 +2387,19 @@
         <v>48</v>
       </c>
       <c r="B71" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" t="s">
         <v>57</v>
       </c>
-      <c r="C71" t="s">
-        <v>59</v>
-      </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E71" t="s">
         <v>55</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2389,19 +2410,19 @@
         <v>48</v>
       </c>
       <c r="B72" t="s">
+        <v>94</v>
+      </c>
+      <c r="C72" t="s">
         <v>57</v>
       </c>
-      <c r="C72" t="s">
-        <v>59</v>
-      </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E72" t="s">
         <v>55</v>
       </c>
       <c r="F72" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -2412,19 +2433,19 @@
         <v>48</v>
       </c>
       <c r="B73" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" t="s">
         <v>57</v>
       </c>
-      <c r="C73" t="s">
-        <v>59</v>
-      </c>
       <c r="D73" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E73" t="s">
         <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2435,19 +2456,19 @@
         <v>48</v>
       </c>
       <c r="B74" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" t="s">
         <v>57</v>
       </c>
-      <c r="C74" t="s">
-        <v>59</v>
-      </c>
       <c r="D74" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E74" t="s">
         <v>55</v>
       </c>
       <c r="F74" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G74">
         <v>3</v>
@@ -2458,19 +2479,19 @@
         <v>48</v>
       </c>
       <c r="B75" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75" t="s">
         <v>57</v>
       </c>
-      <c r="C75" t="s">
-        <v>59</v>
-      </c>
       <c r="D75" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E75" t="s">
         <v>55</v>
       </c>
       <c r="F75" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -2481,19 +2502,19 @@
         <v>48</v>
       </c>
       <c r="B76" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" t="s">
         <v>57</v>
       </c>
-      <c r="C76" t="s">
-        <v>59</v>
-      </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E76" t="s">
         <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -2504,19 +2525,19 @@
         <v>48</v>
       </c>
       <c r="B77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C77" t="s">
         <v>57</v>
       </c>
-      <c r="C77" t="s">
-        <v>59</v>
-      </c>
       <c r="D77" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E77" t="s">
         <v>55</v>
       </c>
       <c r="F77" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G77">
         <v>6</v>
@@ -2527,19 +2548,19 @@
         <v>48</v>
       </c>
       <c r="B78" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" t="s">
         <v>57</v>
       </c>
-      <c r="C78" t="s">
-        <v>59</v>
-      </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E78" t="s">
         <v>55</v>
       </c>
       <c r="F78" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G78">
         <v>7</v>
@@ -2550,21 +2571,228 @@
         <v>48</v>
       </c>
       <c r="B79" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" t="s">
         <v>57</v>
       </c>
-      <c r="C79" t="s">
-        <v>59</v>
-      </c>
       <c r="D79" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E79" t="s">
         <v>55</v>
       </c>
       <c r="F79" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G82" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G83" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G84" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G85" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G86" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G87" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G88" s="4">
         <v>8</v>
       </c>
     </row>
